--- a/data/trans_camb/P32C-Habitat-trans_camb.xlsx
+++ b/data/trans_camb/P32C-Habitat-trans_camb.xlsx
@@ -677,22 +677,22 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-0,34; 2,08</t>
+          <t>-0,44; 2,07</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-0,1; 3,0</t>
+          <t>-0,08; 3,18</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-1,08; 1,04</t>
+          <t>-1,04; 1,02</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,92</t>
+          <t>0,0; 2,73</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -702,22 +702,22 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,12</t>
+          <t>0,0; 3,07</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-0,17; 1,82</t>
+          <t>-0,06; 1,84</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-0,05; 2,28</t>
+          <t>-0,13; 2,05</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-0,5; 1,1</t>
+          <t>-0,39; 1,21</t>
         </is>
       </c>
     </row>
@@ -783,12 +783,12 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-58,8; 992,99</t>
+          <t>-59,58; 902,2</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-47,84; 1395,33</t>
+          <t>-43,98; —</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -813,17 +813,17 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-42,27; 1242,41</t>
+          <t>-42,68; —</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-51,74; —</t>
+          <t>-44,27; —</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-75,63; 789,24</t>
+          <t>-67,57; —</t>
         </is>
       </c>
     </row>
@@ -893,17 +893,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-1,44; 1,28</t>
+          <t>-1,63; 1,36</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-1,43; 1,61</t>
+          <t>-1,42; 1,61</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-1,46; 1,5</t>
+          <t>-1,53; 1,49</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
@@ -913,27 +913,27 @@
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,94</t>
+          <t>0,0; 1,77</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,49; 5,17</t>
+          <t>0,49; 4,82</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-1,04; 0,82</t>
+          <t>-1,05; 0,93</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-0,95; 1,13</t>
+          <t>-0,83; 1,26</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-0,64; 1,88</t>
+          <t>-0,5; 1,98</t>
         </is>
       </c>
     </row>
@@ -999,17 +999,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-70,65; 192,75</t>
+          <t>-71,37; 204,75</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-66,3; 217,62</t>
+          <t>-65,03; 217,35</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-69,29; 201,63</t>
+          <t>-65,84; 209,89</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -1029,17 +1029,17 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-68,56; 206,73</t>
+          <t>-70,33; 201,88</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-66,04; 205,24</t>
+          <t>-61,83; 262,75</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-47,02; 337,16</t>
+          <t>-37,98; 374,06</t>
         </is>
       </c>
     </row>
@@ -1109,17 +1109,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-3,77; 0,95</t>
+          <t>-3,87; 0,93</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-3,86; 0,81</t>
+          <t>-3,99; 1,01</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-4,92; -0,58</t>
+          <t>-5,1; -0,61</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
@@ -1134,22 +1134,22 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,74</t>
+          <t>0,0; 3,92</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-2,7; 0,83</t>
+          <t>-2,86; 0,65</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-3,14; 0,31</t>
+          <t>-3,13; 0,29</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-3,68; -0,13</t>
+          <t>-3,91; -0,38</t>
         </is>
       </c>
     </row>
@@ -1215,17 +1215,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-73,94; 60,22</t>
+          <t>-75,42; 60,52</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-79,83; 49,14</t>
+          <t>-79,53; 61,87</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 1,12</t>
+          <t>-100,0; 4,09</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
@@ -1245,17 +1245,17 @@
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-75,41; 71,13</t>
+          <t>-76,86; 61,34</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-82,5; 41,98</t>
+          <t>-80,5; 37,34</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-96,24; 31,81</t>
+          <t>-100,0; 0,57</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-1,3; 2,82</t>
+          <t>-1,47; 2,64</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-2,93; 0,34</t>
+          <t>-2,8; 0,43</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-2,72; 0,74</t>
+          <t>-2,41; 0,95</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-4,48; -0,44</t>
+          <t>-4,93; -0,35</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-3,97; 0,45</t>
+          <t>-4,12; 0,57</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-4,29; -0,04</t>
+          <t>-4,77; -0,22</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-2,01; 0,95</t>
+          <t>-1,98; 1,04</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-2,72; -0,03</t>
+          <t>-2,5; 0,08</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-2,59; 0,08</t>
+          <t>-2,58; -0,05</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-42,98; 212,2</t>
+          <t>-47,61; 178,91</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-83,15; 34,25</t>
+          <t>-83,26; 46,64</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-76,42; 57,33</t>
+          <t>-72,48; 83,44</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 26,89</t>
+          <t>-100,0; 13,77</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-91,02; 52,72</t>
+          <t>-87,6; 68,28</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-94,15; 11,96</t>
+          <t>-93,14; -0,82</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-62,06; 58,73</t>
+          <t>-60,04; 70,97</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-77,18; 3,19</t>
+          <t>-75,27; 10,07</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-77,82; 15,1</t>
+          <t>-78,29; -1,85</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-0,74; 1,01</t>
+          <t>-0,75; 0,95</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-1,09; 0,55</t>
+          <t>-1,16; 0,55</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-1,51; 0,01</t>
+          <t>-1,47; 0,05</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-1,48; 0,03</t>
+          <t>-1,47; 0,04</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-1,27; 0,37</t>
+          <t>-1,35; 0,37</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-1,06; 0,92</t>
+          <t>-1,13; 0,96</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-0,8; 0,51</t>
+          <t>-0,85; 0,49</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-0,93; 0,27</t>
+          <t>-0,96; 0,29</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-1,14; 0,09</t>
+          <t>-1,13; 0,14</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-31,5; 69,46</t>
+          <t>-32,57; 62,72</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-47,65; 37,29</t>
+          <t>-49,54; 39,03</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-64,87; 4,48</t>
+          <t>-62,75; 6,17</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 69,9</t>
+          <t>-100,0; 49,34</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-82,97; 132,08</t>
+          <t>-85,98; 110,65</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-75,26; 193,9</t>
+          <t>-71,93; 211,17</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-41,22; 41,85</t>
+          <t>-44,43; 40,66</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-48,06; 25,16</t>
+          <t>-48,67; 26,0</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-59,56; 9,12</t>
+          <t>-59,32; 11,59</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/P32C-Habitat-trans_camb.xlsx
+++ b/data/trans_camb/P32C-Habitat-trans_camb.xlsx
@@ -634,7 +634,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>0,08</t>
+          <t>0,06</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -649,7 +649,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,82</t>
+          <t>0,76</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>0,3</t>
+          <t>0,27</t>
         </is>
       </c>
     </row>
@@ -677,22 +677,22 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-0,44; 2,07</t>
+          <t>-0,5; 2,04</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-0,08; 3,18</t>
+          <t>0,01; 3,07</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-1,04; 1,02</t>
+          <t>-0,92; 1,09</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,73</t>
+          <t>0,0; 3,23</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -702,22 +702,22 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,07</t>
+          <t>0,0; 2,71</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-0,06; 1,84</t>
+          <t>-0,18; 1,73</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-0,13; 2,05</t>
+          <t>-0,07; 2,33</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-0,39; 1,21</t>
+          <t>-0,48; 1,07</t>
         </is>
       </c>
     </row>
@@ -740,7 +740,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>13,28%</t>
+          <t>9,29%</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>67,28%</t>
+          <t>59,55%</t>
         </is>
       </c>
     </row>
@@ -783,12 +783,12 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-59,58; 902,2</t>
+          <t>-66,01; —</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-43,98; —</t>
+          <t>-38,78; —</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -813,17 +813,17 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-42,68; —</t>
+          <t>-50,39; —</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-44,27; —</t>
+          <t>-44,25; —</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-67,57; —</t>
+          <t>-76,56; 918,66</t>
         </is>
       </c>
     </row>
@@ -850,7 +850,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>0,02</t>
+          <t>-0,03</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -865,7 +865,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>1,69</t>
+          <t>1,58</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>0,56</t>
+          <t>0,49</t>
         </is>
       </c>
     </row>
@@ -893,17 +893,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-1,63; 1,36</t>
+          <t>-1,51; 1,31</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-1,42; 1,61</t>
+          <t>-1,45; 1,56</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-1,53; 1,49</t>
+          <t>-1,61; 1,36</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
@@ -913,27 +913,27 @@
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,77</t>
+          <t>0,0; 1,42</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,49; 4,82</t>
+          <t>0,46; 4,24</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-1,05; 0,93</t>
+          <t>-1,05; 0,81</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-0,83; 1,26</t>
+          <t>-0,94; 1,11</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-0,5; 1,98</t>
+          <t>-0,51; 1,76</t>
         </is>
       </c>
     </row>
@@ -956,7 +956,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1,41%</t>
+          <t>-2,23%</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>54,85%</t>
+          <t>47,87%</t>
         </is>
       </c>
     </row>
@@ -999,17 +999,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-71,37; 204,75</t>
+          <t>-66,64; 194,03</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-65,03; 217,35</t>
+          <t>-69,32; 236,47</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-65,84; 209,89</t>
+          <t>-73,11; 176,49</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -1029,17 +1029,17 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-70,33; 201,88</t>
+          <t>-70,39; 158,87</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-61,83; 262,75</t>
+          <t>-63,82; 220,72</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-37,98; 374,06</t>
+          <t>-39,41; 344,96</t>
         </is>
       </c>
     </row>
@@ -1066,7 +1066,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>-2,69</t>
+          <t>-2,74</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>0,59</t>
+          <t>1,11</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>-1,79</t>
+          <t>-1,62</t>
         </is>
       </c>
     </row>
@@ -1109,17 +1109,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-3,87; 0,93</t>
+          <t>-3,97; 1,16</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-3,99; 1,01</t>
+          <t>-4,14; 0,78</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-5,1; -0,61</t>
+          <t>-5,42; -0,78</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
@@ -1134,22 +1134,22 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,92</t>
+          <t>0,0; 5,43</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-2,86; 0,65</t>
+          <t>-2,9; 0,81</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-3,13; 0,29</t>
+          <t>-3,14; 0,28</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-3,91; -0,38</t>
+          <t>-3,29; 0,03</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1172,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>-79,57%</t>
+          <t>-81,11%</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>-73,74%</t>
+          <t>-66,82%</t>
         </is>
       </c>
     </row>
@@ -1215,17 +1215,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-75,42; 60,52</t>
+          <t>-75,98; 54,47</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-79,53; 61,87</t>
+          <t>-79,35; 56,79</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 4,09</t>
+          <t>-100,0; -17,33</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
@@ -1245,17 +1245,17 @@
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-76,86; 61,34</t>
+          <t>-75,6; 75,41</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-80,5; 37,34</t>
+          <t>-82,39; 25,9</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 0,57</t>
+          <t>-93,65; 34,47</t>
         </is>
       </c>
     </row>
@@ -1282,7 +1282,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>-0,82</t>
+          <t>-0,71</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -1297,7 +1297,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>-1,88</t>
+          <t>-1,21</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>-1,23</t>
+          <t>-0,9</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-1,47; 2,64</t>
+          <t>-1,34; 2,71</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-2,8; 0,43</t>
+          <t>-2,88; 0,41</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-2,41; 0,95</t>
+          <t>-2,87; 0,78</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-4,93; -0,35</t>
+          <t>-4,81; -0,51</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-4,12; 0,57</t>
+          <t>-4,21; 0,64</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-4,77; -0,22</t>
+          <t>-3,73; 1,55</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-1,98; 1,04</t>
+          <t>-2,08; 1,06</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-2,5; 0,08</t>
+          <t>-2,68; 0,04</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-2,58; -0,05</t>
+          <t>-2,3; 0,68</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>-34,53%</t>
+          <t>-29,79%</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -1403,7 +1403,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>-70,27%</t>
+          <t>-45,08%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>-49,51%</t>
+          <t>-36,08%</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-47,61; 178,91</t>
+          <t>-44,11; 195,81</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-83,26; 46,64</t>
+          <t>-83,57; 43,84</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-72,48; 83,44</t>
+          <t>-79,43; 68,4</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 13,77</t>
+          <t>-100,0; 0,07</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-87,6; 68,28</t>
+          <t>-90,09; 72,49</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-93,14; -0,82</t>
+          <t>-89,14; 171,37</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-60,04; 70,97</t>
+          <t>-61,05; 64,01</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-75,27; 10,07</t>
+          <t>-76,67; 10,47</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-78,29; -1,85</t>
+          <t>-70,26; 48,43</t>
         </is>
       </c>
     </row>
@@ -1498,7 +1498,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>-0,68</t>
+          <t>-0,69</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -1513,7 +1513,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>-0,01</t>
+          <t>0,37</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>-0,49</t>
+          <t>-0,35</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-0,75; 0,95</t>
+          <t>-0,73; 1,02</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-1,16; 0,55</t>
+          <t>-1,13; 0,55</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-1,47; 0,05</t>
+          <t>-1,46; 0,03</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-1,47; 0,04</t>
+          <t>-1,48; 0,01</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-1,35; 0,37</t>
+          <t>-1,37; 0,37</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-1,13; 0,96</t>
+          <t>-0,75; 1,56</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-0,85; 0,49</t>
+          <t>-0,83; 0,47</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-0,96; 0,29</t>
+          <t>-0,94; 0,28</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-1,13; 0,14</t>
+          <t>-0,96; 0,32</t>
         </is>
       </c>
     </row>
@@ -1604,7 +1604,7 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>-36,48%</t>
+          <t>-36,92%</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
@@ -1619,7 +1619,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>-1,52%</t>
+          <t>40,12%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -1634,7 +1634,7 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>-31,23%</t>
+          <t>-22,24%</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-32,57; 62,72</t>
+          <t>-32,44; 67,96</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-49,54; 39,03</t>
+          <t>-48,39; 39,83</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-62,75; 6,17</t>
+          <t>-62,97; 4,23</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 49,34</t>
+          <t>-100,0; 37,17</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-85,98; 110,65</t>
+          <t>-86,14; 107,51</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-71,93; 211,17</t>
+          <t>-60,57; 346,45</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-44,43; 40,66</t>
+          <t>-43,18; 36,61</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-48,67; 26,0</t>
+          <t>-51,12; 23,35</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-59,32; 11,59</t>
+          <t>-50,44; 26,15</t>
         </is>
       </c>
     </row>
